--- a/public/templates/sponsorships_import_template.xlsx
+++ b/public/templates/sponsorships_import_template.xlsx
@@ -186,7 +186,7 @@
     <t>- رقم الملف الخارجي: رقم الملف الخارجي من المؤسسة</t>
   </si>
   <si>
-    <t>- المؤسسة الراعية: اسم المؤسسة التي تقدم الكفالة</t>
+    <t>- اسم الكافل: اسم الكافل/الداعم الذي يقدم الكفالة</t>
   </si>
   <si>
     <t>- تواريخ الكفالة: تنسيق YYYY-MM-DD (مثل: 2024-12-06)</t>
